--- a/BELTRAN 34/Diciembre/Diciembre BELTRAN.xlsx
+++ b/BELTRAN 34/Diciembre/Diciembre BELTRAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BELTRAN 34\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DAFBB44-1435-49C2-98D7-690F29BD287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C33D25-A2A3-4F6E-BB12-DA936289FE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$96</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$97</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="121">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -401,6 +401,9 @@
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </t>
   </si>
+  <si>
+    <t>Traspaso de administracion - Sr. Mara</t>
+  </si>
 </sst>
 </file>
 
@@ -412,8 +415,8 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -1444,7 +1447,7 @@
     <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="33" fillId="17" borderId="29" applyProtection="0"/>
     <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="33" borderId="32" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="26" borderId="33" applyProtection="0"/>
@@ -1455,7 +1458,7 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="35" applyProtection="0"/>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="36" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1628,71 +1631,16 @@
     <xf numFmtId="44" fontId="19" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="43" fillId="2" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="167" fontId="43" fillId="2" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1700,54 +1648,10 @@
     <xf numFmtId="44" fontId="0" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="19" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1760,34 +1664,130 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Énfasis1 2" xfId="4" xr:uid="{E13FD6FD-4381-40A3-9669-15D4AFB54255}"/>
@@ -2183,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2221,68 +2221,68 @@
       <c r="D3" s="97"/>
     </row>
     <row r="4" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A4" s="131" t="s">
+      <c r="A4" s="163" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="131"/>
+      <c r="B4" s="163"/>
       <c r="C4" s="98"/>
       <c r="D4" s="98"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="131"/>
-      <c r="B5" s="131"/>
+      <c r="A5" s="163"/>
+      <c r="B5" s="163"/>
       <c r="C5" s="98"/>
       <c r="D5" s="98"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="131"/>
-      <c r="B6" s="131"/>
+      <c r="A6" s="163"/>
+      <c r="B6" s="163"/>
       <c r="C6" s="98"/>
       <c r="D6" s="98"/>
     </row>
     <row r="7" spans="1:4" ht="13.5" customHeight="1">
-      <c r="A7" s="131"/>
-      <c r="B7" s="131"/>
+      <c r="A7" s="163"/>
+      <c r="B7" s="163"/>
       <c r="C7" s="98"/>
       <c r="D7" s="98"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="B9" s="130" t="s">
+      <c r="B9" s="160" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="B10" s="130"/>
+      <c r="B10" s="160"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="B11" s="130"/>
+      <c r="B11" s="160"/>
     </row>
     <row r="13" spans="1:4" hidden="1"/>
     <row r="14" spans="1:4" ht="15" customHeight="1">
-      <c r="A14" s="132" t="s">
+      <c r="A14" s="164" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="164"/>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1">
-      <c r="A15" s="132"/>
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
+      <c r="A15" s="164"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="164"/>
+      <c r="D15" s="164"/>
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1">
-      <c r="A16" s="132"/>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
+      <c r="A16" s="164"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="164"/>
+      <c r="D16" s="164"/>
     </row>
     <row r="17" spans="1:7" ht="53.25" customHeight="1">
-      <c r="A17" s="132"/>
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
+      <c r="A17" s="164"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="164"/>
+      <c r="D17" s="164"/>
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1">
@@ -2310,16 +2310,16 @@
         <v>110</v>
       </c>
       <c r="B23" s="70"/>
-      <c r="C23" s="180">
+      <c r="C23" s="145">
         <v>131200</v>
       </c>
       <c r="D23" s="70"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="181" t="s">
+      <c r="A24" s="146" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="181"/>
+      <c r="B24" s="146"/>
       <c r="C24" s="95">
         <f>SUM(C23:C23)</f>
         <v>131200</v>
@@ -2351,10 +2351,10 @@
       <c r="D28" s="99"/>
     </row>
     <row r="29" spans="1:7" hidden="1">
-      <c r="A29" s="181" t="s">
+      <c r="A29" s="146" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="182"/>
+      <c r="B29" s="147"/>
       <c r="C29" s="41">
         <f>SUM(C25:C28)</f>
         <v>0</v>
@@ -2384,109 +2384,110 @@
       <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A32" s="144" t="s">
+      <c r="A32" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="B32" s="183"/>
+      <c r="B32" s="148"/>
       <c r="C32" s="111">
         <v>0</v>
       </c>
       <c r="D32" s="109"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="21" customHeight="1">
-      <c r="A33" s="184" t="s">
-        <v>106</v>
-      </c>
-      <c r="B33" s="185"/>
+    <row r="33" spans="1:7" ht="22.5" customHeight="1">
+      <c r="A33" s="128" t="s">
+        <v>120</v>
+      </c>
+      <c r="B33" s="148"/>
       <c r="C33" s="111">
-        <v>80000</v>
+        <v>199000</v>
       </c>
       <c r="D33" s="109"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A34" s="22" t="s">
+    <row r="34" spans="1:7" ht="21" customHeight="1">
+      <c r="A34" s="149" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="150"/>
+      <c r="C34" s="111">
+        <v>80000</v>
+      </c>
+      <c r="D34" s="109"/>
+      <c r="G34" s="12"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A35" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="72">
-        <f>SUM(C32:C33)</f>
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="21" t="s">
+      <c r="B35" s="22"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="72">
+        <f>SUM(C32:C34)</f>
+        <v>279000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="47"/>
-    </row>
-    <row r="36" spans="1:7" s="30" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A36" s="186" t="s">
+      <c r="B36" s="22"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="47"/>
+    </row>
+    <row r="37" spans="1:7" s="30" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A37" s="161" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="187"/>
-      <c r="C36" s="113">
+      <c r="B37" s="162"/>
+      <c r="C37" s="113">
         <v>23077</v>
       </c>
-      <c r="D36" s="108"/>
-    </row>
-    <row r="37" spans="1:7" ht="30" customHeight="1">
-      <c r="A37" s="186" t="s">
+      <c r="D37" s="108"/>
+    </row>
+    <row r="38" spans="1:7" ht="30" customHeight="1">
+      <c r="A38" s="161" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="187"/>
-      <c r="C37" s="114">
+      <c r="B38" s="162"/>
+      <c r="C38" s="114">
         <v>141392</v>
       </c>
-      <c r="D37" s="108"/>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A38" s="22" t="s">
+      <c r="D38" s="108"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A39" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="74">
-        <f>SUM(C36:C37)</f>
+      <c r="B39" s="22"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="74">
+        <f>SUM(C37:C38)</f>
         <v>164469</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
-      <c r="A39" s="21" t="s">
+    <row r="40" spans="1:7" hidden="1">
+      <c r="A40" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="188"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="75"/>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
-      <c r="A40" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" s="115"/>
-      <c r="D40" s="108"/>
-      <c r="F40" s="101"/>
+      <c r="B40" s="152"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="75"/>
     </row>
     <row r="41" spans="1:7" hidden="1">
       <c r="A41" s="70" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="116"/>
+      <c r="C41" s="115"/>
       <c r="D41" s="108"/>
+      <c r="F41" s="101"/>
     </row>
     <row r="42" spans="1:7" hidden="1">
       <c r="A42" s="70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="70" t="s">
         <v>66</v>
@@ -2496,413 +2497,423 @@
     </row>
     <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="70" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="70" t="s">
         <v>66</v>
       </c>
       <c r="C43" s="116"/>
-      <c r="D43" s="107"/>
-    </row>
-    <row r="44" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
-      <c r="A44" s="22" t="s">
+      <c r="D43" s="108"/>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
+      <c r="A44" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="116"/>
+      <c r="D44" s="107"/>
+    </row>
+    <row r="45" spans="1:7" ht="15" hidden="1" customHeight="1" thickBot="1">
+      <c r="A45" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="188"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="74">
-        <f>SUM(C40:C43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="21" t="s">
+      <c r="B45" s="152"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="74">
+        <f>SUM(C41:C44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="188"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="75"/>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A46" s="85" t="s">
+      <c r="B46" s="152"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="75"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1">
+      <c r="A47" s="85" t="s">
         <v>102</v>
       </c>
-      <c r="B46" s="70"/>
-      <c r="C46" s="116">
+      <c r="B47" s="70"/>
+      <c r="C47" s="116">
         <v>50385.73</v>
       </c>
-      <c r="D46" s="106" t="s">
+      <c r="D47" s="106" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A47" s="70" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="70"/>
-      <c r="C47" s="116"/>
-      <c r="D47" s="106"/>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1">
       <c r="A48" s="70" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="70"/>
+      <c r="C48" s="116"/>
+      <c r="D48" s="106"/>
+    </row>
+    <row r="49" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A49" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="70"/>
-      <c r="C48" s="116">
+      <c r="B49" s="70"/>
+      <c r="C49" s="116">
         <v>274519.98</v>
       </c>
-      <c r="D48" s="106" t="s">
+      <c r="D49" s="106" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A49" s="22" t="s">
+    <row r="50" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A50" s="22" t="s">
         <v>3</v>
-      </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="74">
-        <f>SUM(C46:C48)</f>
-        <v>324905.70999999996</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A50" s="21" t="s">
-        <v>31</v>
       </c>
       <c r="B50" s="22"/>
       <c r="C50" s="27"/>
-      <c r="D50" s="77"/>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1">
-      <c r="A51" s="144" t="s">
+      <c r="D50" s="74">
+        <f>SUM(C47:C49)</f>
+        <v>324905.70999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A51" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="22"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="77"/>
+    </row>
+    <row r="52" spans="1:6" ht="30" customHeight="1">
+      <c r="A52" s="128" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="189"/>
-      <c r="C51" s="116">
+      <c r="B52" s="151"/>
+      <c r="C52" s="116">
         <v>73900</v>
-      </c>
-      <c r="D51" s="103" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1">
-      <c r="A52" s="144" t="s">
-        <v>105</v>
-      </c>
-      <c r="B52" s="189"/>
-      <c r="C52" s="116">
-        <v>78900</v>
       </c>
       <c r="D52" s="103" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A53" s="22" t="s">
+    <row r="53" spans="1:6" ht="30" customHeight="1">
+      <c r="A53" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="151"/>
+      <c r="C53" s="116">
+        <v>78900</v>
+      </c>
+      <c r="D53" s="103" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A54" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="80">
-        <f>SUM(C51:C52)</f>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="80">
+        <f>SUM(C52:C53)</f>
         <v>152800</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A54" s="21" t="s">
+    <row r="55" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A55" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="190"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="77"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="70" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" s="70"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="81"/>
+      <c r="B55" s="153"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="77"/>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="70"/>
+      <c r="C56" s="118"/>
+      <c r="D56" s="81"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="B56" s="70"/>
-      <c r="C56" s="116">
+      <c r="B57" s="70"/>
+      <c r="C57" s="116">
         <v>6312.88</v>
       </c>
-      <c r="D56" s="79"/>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A57" s="191" t="s">
+      <c r="D57" s="79"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A58" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="B57" s="191"/>
-      <c r="C57" s="82"/>
-      <c r="D57" s="74">
-        <f>SUM(C55:C56)</f>
+      <c r="B58" s="154"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="74">
+        <f>SUM(C56:C57)</f>
         <v>6312.88</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A58" s="70"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="83"/>
-    </row>
-    <row r="59" spans="1:6" ht="99" customHeight="1" thickBot="1">
-      <c r="A59" s="192" t="s">
+    <row r="59" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A59" s="70"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="83"/>
+    </row>
+    <row r="60" spans="1:6" ht="99" customHeight="1" thickBot="1">
+      <c r="A60" s="166" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="193"/>
-      <c r="C59" s="194"/>
-      <c r="D59" s="84">
-        <f>1800000-859687.59</f>
-        <v>940312.41</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A60" s="195"/>
-      <c r="B60" s="85"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="86"/>
-      <c r="E60" s="35"/>
+      <c r="B60" s="167"/>
+      <c r="C60" s="168"/>
+      <c r="D60" s="84">
+        <f>1800000-859687.59-199000</f>
+        <v>741312.41</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" thickBot="1">
-      <c r="A61" s="196" t="s">
+      <c r="A61" s="155"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="85"/>
+      <c r="D61" s="86"/>
+      <c r="E61" s="35"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A62" s="156" t="s">
         <v>25</v>
       </c>
-      <c r="B61" s="197"/>
-      <c r="C61" s="87"/>
-      <c r="D61" s="88">
-        <f>(SUM(D25:D59))</f>
+      <c r="B62" s="157"/>
+      <c r="C62" s="87"/>
+      <c r="D62" s="88">
+        <f>(SUM(D25:D60))</f>
         <v>1800000</v>
       </c>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="85"/>
-      <c r="B62" s="85"/>
-      <c r="C62" s="85"/>
-      <c r="D62" s="85"/>
-      <c r="F62" s="102"/>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" thickBot="1">
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="85"/>
       <c r="B63" s="85"/>
       <c r="C63" s="85"/>
       <c r="D63" s="85"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="198" t="s">
+      <c r="F63" s="102"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1">
+      <c r="A64" s="85"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="85"/>
+      <c r="D64" s="85"/>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="158" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="199"/>
-      <c r="C64" s="89"/>
-      <c r="D64" s="90"/>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="186"/>
-      <c r="B65" s="187"/>
-      <c r="C65" s="78"/>
-      <c r="D65" s="76"/>
+      <c r="B65" s="159"/>
+      <c r="C65" s="89"/>
+      <c r="D65" s="90"/>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="186"/>
-      <c r="B66" s="187"/>
+      <c r="A66" s="161"/>
+      <c r="B66" s="162"/>
       <c r="C66" s="78"/>
       <c r="D66" s="76"/>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="93"/>
-      <c r="B67" s="94"/>
+      <c r="A67" s="161"/>
+      <c r="B67" s="162"/>
       <c r="C67" s="78"/>
       <c r="D67" s="76"/>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="38"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42">
-        <f>SUM(C65:C67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15" customHeight="1"/>
-    <row r="70" spans="1:4" hidden="1"/>
-    <row r="71" spans="1:4">
-      <c r="A71" s="17" t="s">
+      <c r="A68" s="93"/>
+      <c r="B68" s="94"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="76"/>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="38"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42">
+        <f>SUM(C66:C68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1"/>
+    <row r="71" spans="1:4" hidden="1"/>
+    <row r="72" spans="1:4">
+      <c r="A72" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.75" thickBot="1"/>
-    <row r="73" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A73" s="2" t="s">
+      <c r="B72" s="17"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" thickBot="1"/>
+    <row r="74" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A74" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B73" s="8"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="48">
-        <f>D68+D71</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15.75" thickBot="1"/>
-    <row r="75" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A75" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="B75" s="69">
-        <f>D61</f>
-        <v>1800000</v>
-      </c>
-      <c r="C75" s="35"/>
-    </row>
+      <c r="B74" s="8"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="48">
+        <f>D69+D72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" thickBot="1"/>
     <row r="76" spans="1:4" ht="15.75" thickBot="1">
       <c r="A76" s="68" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B76" s="69">
-        <f>D61-D59</f>
-        <v>859687.59</v>
-      </c>
+        <f>D62</f>
+        <v>1800000</v>
+      </c>
+      <c r="C76" s="35"/>
     </row>
     <row r="77" spans="1:4" ht="15.75" thickBot="1">
       <c r="A77" s="68" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B77" s="69">
-        <f>D73-D71</f>
-        <v>0</v>
+        <f>D62-D60</f>
+        <v>1058687.5899999999</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" thickBot="1">
       <c r="A78" s="68" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" s="69">
+        <f>D74-D72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A79" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="B78" s="69">
-        <f>D73</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A82" s="13" t="s">
+      <c r="B79" s="69">
+        <f>D74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="15.75" thickBot="1">
+      <c r="A83" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B82" s="127"/>
-    </row>
-    <row r="83" spans="1:12" ht="25.5" customHeight="1" thickBot="1">
-      <c r="A83" s="20" t="s">
+      <c r="B83" s="127"/>
+    </row>
+    <row r="84" spans="1:3" ht="25.5" customHeight="1" thickBot="1">
+      <c r="A84" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B83" s="145">
+      <c r="B84" s="129">
         <v>-169461</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A84" s="14" t="s">
+    <row r="85" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A85" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B85" s="32">
         <f>PRORRATEO!H27</f>
-        <v>1303676</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A85" s="14" t="s">
+        <v>1387751.09</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="14.25" customHeight="1">
+      <c r="A86" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B85" s="79">
-        <f>B95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="13.9" customHeight="1">
-      <c r="A86" s="15" t="s">
+      <c r="B86" s="79">
+        <f>B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="13.9" customHeight="1">
+      <c r="A87" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="105"/>
-    </row>
-    <row r="87" spans="1:12">
-      <c r="A87" s="31" t="s">
+      <c r="B87" s="105"/>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B87" s="105">
-        <f>-B76</f>
-        <v>-859687.59</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12">
-      <c r="A88" s="15" t="s">
+      <c r="B88" s="105">
+        <f>-B77</f>
+        <v>-1058687.5899999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B88" s="79">
-        <f>-(B77)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12">
-      <c r="A89" s="19" t="s">
+      <c r="B89" s="79">
+        <f>-(B78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B89" s="146">
-        <f>SUM(B83:B88)</f>
-        <v>274527.41000000003</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="34.5" customHeight="1">
-      <c r="B90" s="33"/>
-      <c r="C90" s="35"/>
-    </row>
-    <row r="91" spans="1:12">
-      <c r="A91" s="129" t="s">
+      <c r="B90" s="130">
+        <f>SUM(B84:B89)</f>
+        <v>159602.50000000023</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="34.5" customHeight="1">
+      <c r="B91" s="33"/>
+      <c r="C91" s="35"/>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="165" t="s">
         <v>46</v>
       </c>
-      <c r="B91" s="129"/>
-    </row>
-    <row r="92" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A92" s="129"/>
-      <c r="B92" s="129"/>
-    </row>
-    <row r="93" spans="1:12" ht="32.25" customHeight="1">
-      <c r="A93" s="91"/>
-      <c r="B93" s="26"/>
-    </row>
-    <row r="94" spans="1:12" ht="32.25" customHeight="1">
+      <c r="B92" s="165"/>
+    </row>
+    <row r="93" spans="1:3" ht="27.75" customHeight="1">
+      <c r="A93" s="165"/>
+      <c r="B93" s="165"/>
+    </row>
+    <row r="94" spans="1:3" ht="32.25" customHeight="1">
       <c r="A94" s="91"/>
       <c r="B94" s="26"/>
     </row>
-    <row r="95" spans="1:12">
-      <c r="A95" s="36" t="s">
+    <row r="95" spans="1:3" ht="32.25" customHeight="1">
+      <c r="A95" s="91"/>
+      <c r="B95" s="26"/>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B95" s="92">
-        <f>SUM(B93:B94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12">
-      <c r="L96" s="6"/>
+      <c r="B96" s="92">
+        <f>SUM(B94:B95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="12:12">
+      <c r="L97" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A92:B93"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A4:B7"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A14:D17"/>
-    <mergeCell ref="A91:B92"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A59:C59"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2938,220 +2949,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.95" customHeight="1">
-      <c r="A1" s="148"/>
-      <c r="B1" s="149" t="str">
+      <c r="A1" s="131"/>
+      <c r="B1" s="169" t="str">
         <f>RESUMEN!A4</f>
         <v xml:space="preserve">Titular: CONSORCIO DE PROPIETARIOS CORONEL BELTRAN 34
 Banco Santander: Cta Corriente en Pesos 533-030591/4
 Cuit del consorcio: 30-71897608-8
 CBU: 0720533020000003059140 - Alias: SALMON.ARMADA.FOCO                                                                                                                                                                                                                                                                                                      </v>
       </c>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="149"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="149"/>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="151"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="133"/>
     </row>
     <row r="2" spans="1:21" ht="33.75" customHeight="1">
-      <c r="A2" s="152"/>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153" t="s">
+      <c r="A2" s="134"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+      <c r="H2" s="170"/>
+      <c r="I2" s="170"/>
+      <c r="J2" s="170"/>
+      <c r="K2" s="170"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="154"/>
-      <c r="O2" s="178">
+      <c r="N2" s="5"/>
+      <c r="O2" s="143">
         <v>1800000</v>
       </c>
-      <c r="P2" s="155"/>
+      <c r="P2" s="136"/>
       <c r="Q2" s="12"/>
     </row>
     <row r="3" spans="1:21" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A3" s="156"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="157"/>
-      <c r="M3" s="157" t="s">
+      <c r="A3" s="137"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="171"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
+      <c r="I3" s="171"/>
+      <c r="J3" s="171"/>
+      <c r="K3" s="171"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138" t="s">
         <v>56</v>
       </c>
-      <c r="N3" s="158"/>
-      <c r="O3" s="179"/>
-      <c r="P3" s="159"/>
+      <c r="N3" s="139"/>
+      <c r="O3" s="144"/>
+      <c r="P3" s="140"/>
     </row>
     <row r="4" spans="1:21" ht="30.6" customHeight="1" thickBot="1">
       <c r="A4" s="5"/>
-      <c r="B4" s="164" t="s">
+      <c r="B4" s="182" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="165"/>
-      <c r="D4" s="165"/>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
-      <c r="K4" s="165"/>
-      <c r="L4" s="165"/>
-      <c r="M4" s="165"/>
-      <c r="N4" s="165"/>
-      <c r="O4" s="165"/>
-      <c r="P4" s="160"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
+      <c r="J4" s="183"/>
+      <c r="K4" s="183"/>
+      <c r="L4" s="183"/>
+      <c r="M4" s="183"/>
+      <c r="N4" s="183"/>
+      <c r="O4" s="183"/>
+      <c r="P4" s="184"/>
     </row>
     <row r="5" spans="1:21" ht="30.6" customHeight="1">
       <c r="A5" s="5"/>
-      <c r="B5" s="169" t="s">
+      <c r="B5" s="185" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="170"/>
-      <c r="K5" s="170"/>
-      <c r="L5" s="170"/>
-      <c r="M5" s="170"/>
-      <c r="N5" s="170"/>
-      <c r="O5" s="170"/>
-      <c r="P5" s="171"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="186"/>
+      <c r="J5" s="186"/>
+      <c r="K5" s="186"/>
+      <c r="L5" s="186"/>
+      <c r="M5" s="186"/>
+      <c r="N5" s="186"/>
+      <c r="O5" s="186"/>
+      <c r="P5" s="187"/>
     </row>
     <row r="6" spans="1:21" ht="30.6" customHeight="1">
       <c r="A6" s="5"/>
-      <c r="B6" s="172"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
-      <c r="H6" s="173"/>
-      <c r="I6" s="173"/>
-      <c r="J6" s="173"/>
-      <c r="K6" s="173"/>
-      <c r="L6" s="173"/>
-      <c r="M6" s="173"/>
-      <c r="N6" s="173"/>
-      <c r="O6" s="173"/>
-      <c r="P6" s="174"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
+      <c r="N6" s="189"/>
+      <c r="O6" s="189"/>
+      <c r="P6" s="190"/>
     </row>
     <row r="7" spans="1:21" ht="155.25" customHeight="1" thickBot="1">
       <c r="A7" s="5"/>
-      <c r="B7" s="175"/>
-      <c r="C7" s="176"/>
-      <c r="D7" s="176"/>
-      <c r="E7" s="176"/>
-      <c r="F7" s="176"/>
-      <c r="G7" s="176"/>
-      <c r="H7" s="176"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="176"/>
-      <c r="N7" s="176"/>
-      <c r="O7" s="176"/>
-      <c r="P7" s="177"/>
+      <c r="B7" s="191"/>
+      <c r="C7" s="192"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
+      <c r="N7" s="192"/>
+      <c r="O7" s="192"/>
+      <c r="P7" s="193"/>
     </row>
     <row r="8" spans="1:21">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="135" t="s">
+      <c r="B8" s="196" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="136" t="s">
+      <c r="C8" s="174" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="136" t="s">
+      <c r="D8" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="136" t="s">
+      <c r="E8" s="174" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="136" t="s">
+      <c r="F8" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="136" t="s">
+      <c r="G8" s="174" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="136" t="s">
+      <c r="H8" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="136" t="s">
+      <c r="I8" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="166" t="s">
+      <c r="J8" s="178" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="142" t="s">
+      <c r="K8" s="176" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="142" t="s">
+      <c r="L8" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="142" t="s">
+      <c r="M8" s="176" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="167" t="s">
+      <c r="N8" s="180" t="s">
         <v>51</v>
       </c>
       <c r="O8" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="P8" s="138" t="s">
+      <c r="P8" s="172" t="s">
         <v>49</v>
       </c>
       <c r="S8" s="35"/>
       <c r="T8" s="33"/>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A9" s="134"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="139"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="136"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="139"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="140"/>
-      <c r="L9" s="142"/>
-      <c r="M9" s="140"/>
-      <c r="N9" s="143"/>
+      <c r="A9" s="195"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="174"/>
+      <c r="G9" s="174"/>
+      <c r="H9" s="174"/>
+      <c r="I9" s="175"/>
+      <c r="J9" s="179"/>
+      <c r="K9" s="177"/>
+      <c r="L9" s="176"/>
+      <c r="M9" s="177"/>
+      <c r="N9" s="181"/>
       <c r="O9" s="43" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/01</v>
       </c>
-      <c r="P9" s="138"/>
+      <c r="P9" s="172"/>
       <c r="S9" s="33">
         <v>65160</v>
       </c>
@@ -3246,7 +3257,7 @@
       <c r="G11" s="50">
         <v>228780</v>
       </c>
-      <c r="H11" s="162">
+      <c r="H11" s="51">
         <f>240131-H21</f>
         <v>228446</v>
       </c>
@@ -3314,7 +3325,7 @@
       <c r="G12" s="51">
         <v>142475</v>
       </c>
-      <c r="H12" s="162">
+      <c r="H12" s="51">
         <f>74400+50775</f>
         <v>125175</v>
       </c>
@@ -3381,7 +3392,7 @@
       <c r="G13" s="50">
         <v>151085</v>
       </c>
-      <c r="H13" s="162"/>
+      <c r="H13" s="51"/>
       <c r="I13" s="52"/>
       <c r="J13" s="53">
         <f t="shared" si="2"/>
@@ -3447,7 +3458,7 @@
       <c r="G14" s="50">
         <v>218940</v>
       </c>
-      <c r="H14" s="162">
+      <c r="H14" s="51">
         <f>G14</f>
         <v>218940</v>
       </c>
@@ -3514,7 +3525,7 @@
       <c r="G15" s="50">
         <v>142475</v>
       </c>
-      <c r="H15" s="162">
+      <c r="H15" s="51">
         <f>154980-H25</f>
         <v>142475</v>
       </c>
@@ -3583,7 +3594,7 @@
       <c r="G16" s="50">
         <v>141245</v>
       </c>
-      <c r="H16" s="162">
+      <c r="H16" s="51">
         <f>G16</f>
         <v>141245</v>
       </c>
@@ -3620,7 +3631,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="R16" s="102"/>
-      <c r="S16" s="163">
+      <c r="S16" s="141">
         <v>64080</v>
       </c>
       <c r="T16" s="33">
@@ -3644,7 +3655,7 @@
       <c r="D17" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="161" t="s">
+      <c r="E17" s="45" t="s">
         <v>113</v>
       </c>
       <c r="F17" s="49">
@@ -3653,7 +3664,7 @@
       <c r="G17" s="50">
         <v>218940</v>
       </c>
-      <c r="H17" s="162">
+      <c r="H17" s="51">
         <f>G17</f>
         <v>218940</v>
       </c>
@@ -3720,18 +3731,18 @@
       <c r="G18" s="51">
         <v>142475</v>
       </c>
-      <c r="H18" s="168">
-        <f>41700</f>
-        <v>41700</v>
+      <c r="H18" s="142">
+        <f>41700+84075.09</f>
+        <v>125775.09</v>
       </c>
       <c r="I18" s="52"/>
       <c r="J18" s="122">
         <f t="shared" si="2"/>
-        <v>100775</v>
+        <v>16699.910000000003</v>
       </c>
       <c r="K18" s="122">
         <f t="shared" si="3"/>
-        <v>3023.25</v>
+        <v>500.99730000000011</v>
       </c>
       <c r="L18" s="123">
         <f t="shared" si="4"/>
@@ -3746,11 +3757,11 @@
       </c>
       <c r="O18" s="125">
         <f t="shared" si="6"/>
-        <v>228898.09</v>
+        <v>142301.09</v>
       </c>
       <c r="P18" s="126">
         <f t="shared" si="0"/>
-        <v>235765.09</v>
+        <v>146570.09</v>
       </c>
       <c r="Q18" s="35">
         <f t="shared" si="7"/>
@@ -3789,7 +3800,7 @@
       <c r="G19" s="50">
         <v>141245</v>
       </c>
-      <c r="H19" s="162">
+      <c r="H19" s="51">
         <f>G19</f>
         <v>141245</v>
       </c>
@@ -3856,7 +3867,7 @@
       <c r="G20" s="50">
         <v>243540</v>
       </c>
-      <c r="H20" s="162"/>
+      <c r="H20" s="51"/>
       <c r="I20" s="52"/>
       <c r="J20" s="53">
         <f t="shared" si="2"/>
@@ -3920,7 +3931,7 @@
       <c r="G21" s="50">
         <v>11685</v>
       </c>
-      <c r="H21" s="162">
+      <c r="H21" s="51">
         <f>G21</f>
         <v>11685</v>
       </c>
@@ -3987,7 +3998,7 @@
       <c r="G22" s="50">
         <v>10660</v>
       </c>
-      <c r="H22" s="162">
+      <c r="H22" s="51">
         <f>G22</f>
         <v>10660</v>
       </c>
@@ -4054,7 +4065,7 @@
       <c r="G23" s="50">
         <v>10660</v>
       </c>
-      <c r="H23" s="162">
+      <c r="H23" s="51">
         <f>G23</f>
         <v>10660</v>
       </c>
@@ -4121,7 +4132,7 @@
       <c r="G24" s="50">
         <v>10660</v>
       </c>
-      <c r="H24" s="162"/>
+      <c r="H24" s="51"/>
       <c r="I24" s="52"/>
       <c r="J24" s="53">
         <f t="shared" si="2"/>
@@ -4185,7 +4196,7 @@
       <c r="G25" s="50">
         <v>12505</v>
       </c>
-      <c r="H25" s="162">
+      <c r="H25" s="51">
         <f>G25</f>
         <v>12505</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="H27" s="44">
         <f>SUM(H10:H26)</f>
-        <v>1303676</v>
+        <v>1387751.09</v>
       </c>
       <c r="I27" s="44">
         <f>SUM(I10:I26)</f>
@@ -4306,11 +4317,11 @@
       </c>
       <c r="O27" s="67">
         <f>SUM(O10:O25)</f>
-        <v>5141123.3599999994</v>
+        <v>5054526.3599999994</v>
       </c>
       <c r="P27" s="67">
         <f>SUM(P10:P25)</f>
-        <v>5295358.3599999994</v>
+        <v>5206163.3599999994</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="12.75" customHeight="1">
@@ -4319,93 +4330,98 @@
     </row>
     <row r="29" spans="1:21" ht="15" hidden="1" customHeight="1"/>
     <row r="30" spans="1:21" ht="9" customHeight="1">
-      <c r="D30" s="128" t="s">
+      <c r="D30" s="173" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="128"/>
-      <c r="F30" s="128"/>
-      <c r="G30" s="128"/>
-      <c r="H30" s="128"/>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="128"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="128"/>
-      <c r="O30" s="128"/>
+      <c r="E30" s="173"/>
+      <c r="F30" s="173"/>
+      <c r="G30" s="173"/>
+      <c r="H30" s="173"/>
+      <c r="I30" s="173"/>
+      <c r="J30" s="173"/>
+      <c r="K30" s="173"/>
+      <c r="L30" s="173"/>
+      <c r="M30" s="173"/>
+      <c r="N30" s="173"/>
+      <c r="O30" s="173"/>
     </row>
     <row r="31" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D31" s="128"/>
-      <c r="E31" s="128"/>
-      <c r="F31" s="128"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="128"/>
-      <c r="I31" s="128"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="128"/>
-      <c r="M31" s="128"/>
-      <c r="N31" s="128"/>
-      <c r="O31" s="128"/>
+      <c r="D31" s="173"/>
+      <c r="E31" s="173"/>
+      <c r="F31" s="173"/>
+      <c r="G31" s="173"/>
+      <c r="H31" s="173"/>
+      <c r="I31" s="173"/>
+      <c r="J31" s="173"/>
+      <c r="K31" s="173"/>
+      <c r="L31" s="173"/>
+      <c r="M31" s="173"/>
+      <c r="N31" s="173"/>
+      <c r="O31" s="173"/>
     </row>
     <row r="32" spans="1:21" ht="12" hidden="1" customHeight="1">
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
-      <c r="F32" s="128"/>
-      <c r="G32" s="128"/>
-      <c r="H32" s="128"/>
-      <c r="I32" s="128"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
-      <c r="O32" s="128"/>
+      <c r="D32" s="173"/>
+      <c r="E32" s="173"/>
+      <c r="F32" s="173"/>
+      <c r="G32" s="173"/>
+      <c r="H32" s="173"/>
+      <c r="I32" s="173"/>
+      <c r="J32" s="173"/>
+      <c r="K32" s="173"/>
+      <c r="L32" s="173"/>
+      <c r="M32" s="173"/>
+      <c r="N32" s="173"/>
+      <c r="O32" s="173"/>
     </row>
     <row r="33" spans="4:15" ht="12" hidden="1" customHeight="1">
-      <c r="D33" s="128"/>
-      <c r="E33" s="128"/>
-      <c r="F33" s="128"/>
-      <c r="G33" s="128"/>
-      <c r="H33" s="128"/>
-      <c r="I33" s="128"/>
-      <c r="J33" s="128"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
-      <c r="M33" s="128"/>
-      <c r="N33" s="128"/>
-      <c r="O33" s="128"/>
+      <c r="D33" s="173"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="173"/>
+      <c r="G33" s="173"/>
+      <c r="H33" s="173"/>
+      <c r="I33" s="173"/>
+      <c r="J33" s="173"/>
+      <c r="K33" s="173"/>
+      <c r="L33" s="173"/>
+      <c r="M33" s="173"/>
+      <c r="N33" s="173"/>
+      <c r="O33" s="173"/>
     </row>
     <row r="34" spans="4:15" ht="12" hidden="1" customHeight="1">
-      <c r="D34" s="128"/>
-      <c r="E34" s="128"/>
-      <c r="F34" s="128"/>
-      <c r="G34" s="128"/>
-      <c r="H34" s="128"/>
-      <c r="I34" s="128"/>
-      <c r="J34" s="128"/>
-      <c r="K34" s="128"/>
-      <c r="L34" s="128"/>
-      <c r="M34" s="128"/>
-      <c r="N34" s="128"/>
-      <c r="O34" s="128"/>
+      <c r="D34" s="173"/>
+      <c r="E34" s="173"/>
+      <c r="F34" s="173"/>
+      <c r="G34" s="173"/>
+      <c r="H34" s="173"/>
+      <c r="I34" s="173"/>
+      <c r="J34" s="173"/>
+      <c r="K34" s="173"/>
+      <c r="L34" s="173"/>
+      <c r="M34" s="173"/>
+      <c r="N34" s="173"/>
+      <c r="O34" s="173"/>
     </row>
     <row r="35" spans="4:15" ht="65.25" customHeight="1">
-      <c r="D35" s="128"/>
-      <c r="E35" s="128"/>
-      <c r="F35" s="128"/>
-      <c r="G35" s="128"/>
-      <c r="H35" s="128"/>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="128"/>
-      <c r="O35" s="128"/>
+      <c r="D35" s="173"/>
+      <c r="E35" s="173"/>
+      <c r="F35" s="173"/>
+      <c r="G35" s="173"/>
+      <c r="H35" s="173"/>
+      <c r="I35" s="173"/>
+      <c r="J35" s="173"/>
+      <c r="K35" s="173"/>
+      <c r="L35" s="173"/>
+      <c r="M35" s="173"/>
+      <c r="N35" s="173"/>
+      <c r="O35" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="F8:F9"/>
     <mergeCell ref="B1:K3"/>
     <mergeCell ref="P8:P9"/>
     <mergeCell ref="D30:O35"/>
@@ -4420,11 +4436,6 @@
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="B5:P7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="F8:F9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="5" orientation="landscape" r:id="rId1"/>
